--- a/media/temp_planning.xlsx
+++ b/media/temp_planning.xlsx
@@ -202,11 +202,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="44.550000000000004" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="51.300000000000004" customWidth="1"/>
-    <col min="4" max="4" width="47.25" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="24.3" customWidth="1"/>
+    <col min="2" max="2" width="47.25" customWidth="1"/>
+    <col min="3" max="3" width="24.3" customWidth="1"/>
+    <col min="4" max="4" width="24.3" customWidth="1"/>
+    <col min="5" max="5" width="24.3" customWidth="1"/>
+    <col min="6" max="6" width="40.5" customWidth="1"/>
     <col min="7" max="7" width="24.3" customWidth="1"/>
     <col min="8" max="8" width="24.3" customWidth="1"/>
     <col min="9" max="9" width="40.5" customWidth="1"/>
@@ -227,37 +227,37 @@
       </c>
       <c t="inlineStr" r="B2" s="2">
         <is>
-          <t xml:space="preserve">Lundi 16/02</t>
+          <t xml:space="preserve">Lundi  2/02</t>
         </is>
       </c>
       <c t="inlineStr" r="C2" s="2">
         <is>
-          <t xml:space="preserve">Mardi 17/02</t>
+          <t xml:space="preserve">Mardi  3/02</t>
         </is>
       </c>
       <c t="inlineStr" r="D2" s="2">
         <is>
-          <t xml:space="preserve">Mercredi 18/02</t>
+          <t xml:space="preserve">Mercredi  4/02</t>
         </is>
       </c>
       <c t="inlineStr" r="E2" s="2">
         <is>
-          <t xml:space="preserve">Jeudi 19/02</t>
+          <t xml:space="preserve">Jeudi  5/02</t>
         </is>
       </c>
       <c t="inlineStr" r="F2" s="2">
         <is>
-          <t xml:space="preserve">Vendredi 20/02</t>
+          <t xml:space="preserve">Vendredi  6/02</t>
         </is>
       </c>
       <c t="inlineStr" r="G2" s="2">
         <is>
-          <t xml:space="preserve">Samedi 21/02</t>
+          <t xml:space="preserve">Samedi  7/02</t>
         </is>
       </c>
       <c t="inlineStr" r="H2" s="2">
         <is>
-          <t xml:space="preserve">Dimanche 22/02</t>
+          <t xml:space="preserve">Dimanche  8/02</t>
         </is>
       </c>
       <c t="inlineStr" r="I2" s="2">
@@ -274,27 +274,27 @@
       </c>
       <c t="inlineStr" r="B3">
         <is>
+          <t xml:space="preserve">8h-16h R 16h-19h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C3">
+        <is>
           <t xml:space="preserve">8h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C3">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D3">
         <is>
-          <t xml:space="preserve">CH 10h-16h R 10h-16h</t>
+          <t xml:space="preserve">8h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">8h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">8h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
@@ -321,27 +321,27 @@
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">13h-22h R 22h-23h R 23h-2h R 2h-3h R 3h-4h50</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">CH 16h30-0h30 R 16h30-0h30</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D4">
         <is>
-          <t xml:space="preserve">CH 14h-23h R 14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
@@ -430,12 +430,12 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
@@ -462,37 +462,37 @@
       </c>
       <c t="inlineStr" r="B7">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C7">
+        <is>
+          <t xml:space="preserve">MISE À PIED</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D7">
+        <is>
+          <t xml:space="preserve">MISE À PIED</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E7">
+        <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C7">
+      <c t="inlineStr" r="F7">
         <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D7">
-        <is>
-          <t xml:space="preserve">14h-23h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E7">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F7">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
@@ -519,17 +519,17 @@
       </c>
       <c t="inlineStr" r="D8">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G8">
@@ -556,37 +556,37 @@
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D9">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E9">
+        <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D9">
-        <is>
-          <t xml:space="preserve">R 15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E9">
+      <c t="inlineStr" r="F9">
         <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F9">
+      <c t="inlineStr" r="G9">
         <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="G9">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
@@ -603,14 +603,14 @@
       </c>
       <c t="inlineStr" r="B10">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C10">
+        <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C10">
-        <is>
-          <t xml:space="preserve">14h-23h P 16h30-16h50</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D10">
         <is>
           <t xml:space="preserve">14h-23h</t>
@@ -618,22 +618,22 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
@@ -650,12 +650,12 @@
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">21h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">21h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D11">
@@ -692,37 +692,37 @@
       </c>
       <c t="inlineStr" r="B12">
         <is>
+          <t xml:space="preserve">6h-16h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C12">
+        <is>
           <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C12">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D12">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E12">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F12">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G12">
+        <is>
           <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F12">
+      <c t="inlineStr" r="H12">
         <is>
           <t xml:space="preserve">6h-16h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G12">
-        <is>
-          <t xml:space="preserve">15h-1h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H12">
-        <is>
-          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
@@ -739,37 +739,37 @@
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">R 19h-3h R 3h-4h50</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">R 17h-18h 18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D13">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
@@ -786,19 +786,19 @@
       </c>
       <c t="inlineStr" r="B14">
         <is>
+          <t xml:space="preserve">8h-18h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
           <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C14">
+      <c t="inlineStr" r="D14">
         <is>
           <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D14">
-        <is>
-          <t xml:space="preserve">17h-3h</t>
-        </is>
-      </c>
       <c t="inlineStr" r="E14">
         <is>
           <t xml:space="preserve">REPOS</t>
@@ -806,17 +806,17 @@
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
@@ -833,17 +833,17 @@
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">CH 5h-13h R 5h-13h</t>
+          <t xml:space="preserve">5h-14h CH 16h10-18h10 R 16h10-18h10</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">5h-14h CH 17h-19h R 17h-19h</t>
+          <t xml:space="preserve">CH 5h-12h R 5h-12h</t>
         </is>
       </c>
       <c t="inlineStr" r="D15">
         <is>
-          <t xml:space="preserve">5h-14h CH 15h20-17h20 R 15h20-17h20</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E15">
@@ -858,12 +858,12 @@
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
@@ -880,37 +880,37 @@
       </c>
       <c t="inlineStr" r="B16">
         <is>
+          <t xml:space="preserve">7h-16h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C16">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D16">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="E16">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F16">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G16">
+        <is>
           <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F16">
+      <c t="inlineStr" r="H16">
         <is>
           <t xml:space="preserve">7h-16h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G16">
-        <is>
-          <t xml:space="preserve">12h-21h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H16">
-        <is>
-          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
@@ -932,22 +932,22 @@
       </c>
       <c t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h CH 17h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D17">
         <is>
-          <t xml:space="preserve">R 20h-1h CH 20h-1h</t>
+          <t xml:space="preserve">16h-1h CH 17h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">16h-1h CH 17h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">16h-1h CH 17h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G17">
@@ -974,37 +974,37 @@
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">R 18h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D18">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E18">
+        <is>
+          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F18">
+        <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D18">
+      <c t="inlineStr" r="G18">
         <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E18">
+      <c t="inlineStr" r="H18">
         <is>
           <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F18">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G18">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H18">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I18">
@@ -1115,37 +1115,37 @@
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">7h-16h P 8h25-10h25</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D21">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E21">
+        <is>
           <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E21">
+      <c t="inlineStr" r="F21">
         <is>
           <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F21">
+      <c t="inlineStr" r="G21">
         <is>
           <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="G21">
-        <is>
-          <t xml:space="preserve">R 12h-14h</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
@@ -1157,32 +1157,32 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Bayram (Bayrem SAYEH)</t>
+          <t xml:space="preserve">Aziz (Abdelaziz bilel BRAHAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
@@ -1197,96 +1197,96 @@
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t xml:space="preserve">Technicien</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Betty (Soulef BEN AMOR)</t>
+          <t xml:space="preserve">Bayram (Bayrem SAYEH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">CH 6h-11h R 6h-11h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Technicien</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">Brann (Marwen HOSNI)</t>
+          <t xml:space="preserve">Betty (Soulef BEN AMOR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">V 14h-18h R 18h-22h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">14h-23h R 23h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
@@ -1298,42 +1298,42 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">Briana (Latifa BEN MANSOUR)</t>
+          <t xml:space="preserve">Brann (Marwen HOSNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">18h-3h R 3h-4h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D25">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">V 14h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
@@ -1345,32 +1345,32 @@
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">Britney (Wided LAAROUSSI)</t>
+          <t xml:space="preserve">Briana (Latifa BEN MANSOUR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">CH 16h-22h R 16h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D26">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
@@ -1380,34 +1380,39 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">Brooklyn (Soumaya ZAALOUNI)</t>
+          <t xml:space="preserve">Britney (Wided LAAROUSSI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="D27">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1417,39 +1422,34 @@
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">14h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I27">
-        <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">Bruce (Kacem ROMDHANI)</t>
+          <t xml:space="preserve">Brooklyn (Soumaya ZAALOUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D28">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E28">
@@ -1464,106 +1464,106 @@
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Carla (Saida ABDELLI)</t>
+          <t xml:space="preserve">Bruce (Kacem ROMDHANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D29">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">Cedric (Amine ASKRI)</t>
+          <t xml:space="preserve">Carla (Saida ABDELLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D30">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
@@ -1575,42 +1575,42 @@
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">Cersei (Khaoula BRAHIM)</t>
+          <t xml:space="preserve">Cedric (Amine ASKRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">18h-3h R 3h-4h50</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D31">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
@@ -1622,101 +1622,101 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">Cesar (Mohamed BOUCHIBA)</t>
+          <t xml:space="preserve">Cersei (Khaoula BRAHIM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D32">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">Chafika (Chafika CHAOUECH)</t>
+          <t xml:space="preserve">Cesar (Mohamed BOUCHIBA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D33">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">Chloe (Jihene BOUSLAMA)</t>
+          <t xml:space="preserve">Chafika (Chafika CHAOUECH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
@@ -1726,44 +1726,44 @@
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="D34">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Colin (Marwen BAGHDADI)</t>
+          <t xml:space="preserve">Chloe (Jihene BOUSLAMA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
@@ -1810,225 +1810,225 @@
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">Collins (Lotfi BOUDHIB)</t>
+          <t xml:space="preserve">Colin (Marwen BAGHDADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D36">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I36">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">Cora (Manel GAFSAOUI)</t>
+          <t xml:space="preserve">Collins (Lotfi BOUDHIB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D37">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">7h-16h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I37">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">Damen (Nour CHELLY)</t>
+          <t xml:space="preserve">Cora (Manel GAFSAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D38">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">Damien (Hatem BEN ZINEB)</t>
+          <t xml:space="preserve">Damen (Nour CHELLY)</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">R+ 14h-15h 15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D39">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">R 12h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 16h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">Darius (Mejdi EL AYED)</t>
+          <t xml:space="preserve">Damien (Hatem BEN ZINEB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D40">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I40">
@@ -2040,7 +2040,7 @@
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Davina (Arwa JOUBID)</t>
+          <t xml:space="preserve">Darius (Mejdi EL AYED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
@@ -2060,7 +2060,7 @@
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">CH 11h-17h R 11h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
@@ -2087,7 +2087,7 @@
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Deborah (Najla AHMED)</t>
+          <t xml:space="preserve">Davina (Arwa JOUBID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
@@ -2097,22 +2097,22 @@
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D42">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
@@ -2134,42 +2134,42 @@
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">Diane (Radhia CHAKROUN)</t>
+          <t xml:space="preserve">Deborah (Najla AHMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-15h F 15h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D43">
         <is>
-          <t xml:space="preserve">F 13h-14h 14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-15h F 15h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">R 18h-22h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
@@ -2181,22 +2181,22 @@
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">Donis (Houcem EL GHOUL)</t>
+          <t xml:space="preserve">Diane (Radhia CHAKROUN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">14h-23h R 23h-0h</t>
+          <t xml:space="preserve">R 19h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">R 8h-14h</t>
+          <t xml:space="preserve">F 13h-14h 14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D44">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E44">
@@ -2211,12 +2211,12 @@
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
@@ -2228,22 +2228,22 @@
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">Doris (Rihab SGHAIR)</t>
+          <t xml:space="preserve">Donis (Houcem EL GHOUL)</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D45">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E45">
@@ -2258,12 +2258,12 @@
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
@@ -2275,42 +2275,42 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Dustin (Faeez HENI)</t>
+          <t xml:space="preserve">Doris (Rihab SGHAIR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D46">
         <is>
-          <t xml:space="preserve">13h-22h R 22h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
@@ -2322,54 +2322,49 @@
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Eddy (Hamdi CHERIF)</t>
+          <t xml:space="preserve">Drake (Mohamed bechir BEZI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">17h-2h R 2h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D47">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">15h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">17h-2h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I47">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">15h-19h</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Elena (Ines CHOUCHANNE)</t>
+          <t xml:space="preserve">Dustin (Faeez HENI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
@@ -2379,22 +2374,22 @@
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D48">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
@@ -2416,42 +2411,42 @@
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Emile (Franck roland danie N'DRI)</t>
+          <t xml:space="preserve">Eddy (Hamdi CHERIF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D49">
         <is>
-          <t xml:space="preserve">R 9h-18h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
@@ -2463,89 +2458,89 @@
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Emilio (Ahmed HOURY)</t>
+          <t xml:space="preserve">Elena (Ines CHOUCHANNE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D50">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">Formateur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Enola (Khouloud FARJALLAH)</t>
+          <t xml:space="preserve">Emile (Franck roland danie N'DRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">R 13h-14h52</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D51">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
@@ -2557,74 +2552,74 @@
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Esther (Amal GALBI)</t>
+          <t xml:space="preserve">Emilio (Ahmed HOURY)</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="D52">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Formateur</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Evan (Rochdi LARIBI)</t>
+          <t xml:space="preserve">Enola (Khouloud FARJALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D53">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 15h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
@@ -2634,12 +2629,12 @@
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
@@ -2651,89 +2646,89 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Eve (Ons BEN AMOR)</t>
+          <t xml:space="preserve">Esther (Amal GALBI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D54">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Evita (Imen NASRAOUI)</t>
+          <t xml:space="preserve">Evan (Rochdi LARIBI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
@@ -2745,89 +2740,89 @@
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Fabrice (Mohamed ridha FRADI)</t>
+          <t xml:space="preserve">Eve (Ons BEN AMOR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D56">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">R 9h-15h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Felix (Mohamed MANSOURI)</t>
+          <t xml:space="preserve">Evita (Imen NASRAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">R 18h05-3h05</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="D57">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
@@ -2839,64 +2834,64 @@
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Feriel (Feriel SGHAIER)</t>
+          <t xml:space="preserve">Fabrice (Mohamed ridha FRADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
+          <t xml:space="preserve">8h-17h R 19h-21h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D58">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E58">
+        <is>
           <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C58">
+      <c t="inlineStr" r="F58">
         <is>
           <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D58">
+      <c t="inlineStr" r="G58">
         <is>
           <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E58">
+      <c t="inlineStr" r="H58">
         <is>
           <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F58">
-        <is>
-          <t xml:space="preserve">8h-17h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G58">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H58">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">Auditeur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Fiona (Faieza ESSID)</t>
+          <t xml:space="preserve">Felix (Mohamed MANSOURI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D59">
@@ -2906,59 +2901,59 @@
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Galia (Nahla AYADI)</t>
+          <t xml:space="preserve">Feriel (Feriel SGHAIER)</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">CH 17h-23h R 17h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">12h-21h CH 21h-22h R 21h-22h R 22h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D60">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G60">
@@ -2973,49 +2968,49 @@
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Auditeur</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Gwen (Ghalia FRAJ)</t>
+          <t xml:space="preserve">Fiona (Faieza ESSID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D61">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
@@ -3027,101 +3022,101 @@
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Hannah (Hanedi NASR)</t>
+          <t xml:space="preserve">Galia (Nahla AYADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D62">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">Auditeur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Harry (Mohamed nacer JDIDI)</t>
+          <t xml:space="preserve">Gwen (Ghalia FRAJ)</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">R 20h-3h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">V 17h15-18h 18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D63">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="G63">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Holly (Khouloud ZAMMEL)</t>
+          <t xml:space="preserve">Hannah (Hanedi NASR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
@@ -3131,22 +3126,22 @@
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">17h-2h R 2h-3h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D64">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
@@ -3161,19 +3156,19 @@
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Auditeur</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Ilhem  (Ilhem FAIECH)</t>
+          <t xml:space="preserve">Harry (Mohamed nacer JDIDI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C65">
@@ -3183,74 +3178,74 @@
       </c>
       <c t="inlineStr" r="D65">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Imane (Imen HANI)</t>
+          <t xml:space="preserve">Holly (Khouloud ZAMMEL)</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">9h-17h R 20h-22h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D66">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
@@ -3262,79 +3257,79 @@
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Iris (Amal FRADI NÉE DARDOUR)</t>
+          <t xml:space="preserve">Ilhem  (Ilhem FAIECH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D67">
         <is>
-          <t xml:space="preserve">8h-17h R 19h-20h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">8h-17h R 19h-21h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
         <is>
-          <t xml:space="preserve">R 9h-15h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Irma (Insaf LETAIEF)</t>
+          <t xml:space="preserve">Imane (Imen HANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D68">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E68">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
@@ -3356,106 +3351,106 @@
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Isaac (Salem BEN SLAMA)</t>
+          <t xml:space="preserve">Iris (Amal FRADI NÉE DARDOUR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-17h R 19h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">R 19h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="D69">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E69">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t xml:space="preserve">Créateur de contenu multimédia</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Isacc (Anis MOKNI)</t>
+          <t xml:space="preserve">Irma (Insaf LETAIEF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D70">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E70">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G70">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Jade (Ouejdene OUERGHI)</t>
+          <t xml:space="preserve">Isaac (Salem BEN SLAMA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">22h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C71">
@@ -3465,49 +3460,49 @@
       </c>
       <c t="inlineStr" r="D71">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E71">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F71">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G71">
         <is>
-          <t xml:space="preserve">22h-7h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">22h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Créateur de contenu multimédia</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Jaime (Achref MLOUKA)</t>
+          <t xml:space="preserve">Isacc (Anis MOKNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">15h-0h R 0h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">R 20h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D72">
@@ -3517,49 +3512,49 @@
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="G72">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Jairo (Mohamed KHAIR EDDINE)</t>
+          <t xml:space="preserve">Jade (Ouejdene OUERGHI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="D73">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="E73">
@@ -3569,49 +3564,49 @@
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">R 20h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">James (Anouar ATTIA)</t>
+          <t xml:space="preserve">Jaime (Achref MLOUKA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">R 14h-17h 17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">F 13h-14h R 14h-17h 17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D74">
         <is>
-          <t xml:space="preserve">R 14h-17h 17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E74">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F74">
@@ -3621,12 +3616,12 @@
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">R 14h-17h 17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t xml:space="preserve">R 14h-17h 17h-2h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
@@ -3638,32 +3633,32 @@
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">Jamila  (Jamila HANZOULI)</t>
+          <t xml:space="preserve">Jairo (Mohamed KHAIR EDDINE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">F 15h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D75">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E75">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G75">
@@ -3673,54 +3668,54 @@
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Javier (Mohamed iheb ASKRI)</t>
+          <t xml:space="preserve">James (Anouar ATTIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">F 15h-16h 16h-1h</t>
+          <t xml:space="preserve">F 13h-14h R 14h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D76">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">F 16h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">F 16h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I76">
@@ -3732,22 +3727,22 @@
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Joaquin (Nassim BEN AZIZA)</t>
+          <t xml:space="preserve">Jamila  (Jamila HANZOULI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
+          <t xml:space="preserve">11h-20h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C77">
-        <is>
-          <t xml:space="preserve">R 6h11-10h11</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D77">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E77">
@@ -3762,59 +3757,59 @@
       </c>
       <c t="inlineStr" r="G77">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Jocelyne (Soraya AISSA)</t>
+          <t xml:space="preserve">Javier (Mohamed iheb ASKRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">R 9h-13h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D78">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E78">
         <is>
-          <t xml:space="preserve">7h-13h 19h-22h</t>
+          <t xml:space="preserve">F 16h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">7h-13h 19h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G78">
         <is>
-          <t xml:space="preserve">7h-13h 19h-22h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">7h-13h 19h-22h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I78">
@@ -3826,7 +3821,7 @@
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">John (Mohamed MOKNI)</t>
+          <t xml:space="preserve">Joaquin (Nassim BEN AZIZA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
@@ -3851,7 +3846,7 @@
       </c>
       <c t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">R 6h30-12h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G79">
@@ -3873,42 +3868,42 @@
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">Jolaine (Amira AOUINA)</t>
+          <t xml:space="preserve">Jocelyne (Soraya AISSA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I80">
@@ -3920,42 +3915,42 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Jonas (Younes GHABRI)</t>
+          <t xml:space="preserve">John (Mohamed MOKNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">R 15h-16h 16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D81">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E81">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G81">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H81">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I81">
@@ -3967,42 +3962,42 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Jules (Hefdhi BRAHEM)</t>
+          <t xml:space="preserve">Jolaine (Amira AOUINA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">R 12h-14h CH 12h-0h 14h-23h R 23h-0h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">R 13h-14h CH 13h-0h 14h-23h R 23h-0h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="D82">
         <is>
-          <t xml:space="preserve">R 12h-14h CH 12h-23h 14h-23h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="E82">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="G82">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="H82">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="I82">
@@ -4014,42 +4009,42 @@
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Julienne (Samia HAMROUNI)</t>
+          <t xml:space="preserve">Jonas (Younes GHABRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">R 15h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I83">
@@ -4061,126 +4056,126 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Kamilla (Khadija SOUISSI)</t>
+          <t xml:space="preserve">Jules (Hefdhi BRAHEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D84">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E84">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I84">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Karim (Karim SELLAM)</t>
+          <t xml:space="preserve">Julienne (Samia HAMROUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D85">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="E85">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="I85">
         <is>
-          <t xml:space="preserve">Technicien</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Karl (Nour elyakin MBARKI)</t>
+          <t xml:space="preserve">Kamilla (Khadija SOUISSI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">R 16h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="D86">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="E86">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="G86">
@@ -4195,39 +4190,39 @@
       </c>
       <c t="inlineStr" r="I86">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Kayn (Tarek JLASSI MONASTIRI)</t>
+          <t xml:space="preserve">Karim (Karim SELLAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D87">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E87">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G87">
@@ -4242,49 +4237,49 @@
       </c>
       <c t="inlineStr" r="I87">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Technicien</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Kenzo (Mohamed khairi MRIZAK)</t>
+          <t xml:space="preserve">Karl (Nour elyakin MBARKI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">R 19h30-1h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">14h-23h R 23h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D88">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E88">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G88">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H88">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I88">
@@ -4296,59 +4291,59 @@
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Kim (Imen AMERI)</t>
+          <t xml:space="preserve">Kayn (Tarek JLASSI MONASTIRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">R 19h45-23h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D89">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E89">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G89">
         <is>
-          <t xml:space="preserve">R 18h-21h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I89">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Kisha (Sondes AMARA)</t>
+          <t xml:space="preserve">Kenzo (Mohamed khairi MRIZAK)</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C90">
@@ -4358,27 +4353,27 @@
       </c>
       <c t="inlineStr" r="D90">
         <is>
-          <t xml:space="preserve">CH 14h-23h V 14h-18h R 18h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E90">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I90">
@@ -4390,42 +4385,42 @@
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Kylian (Hassan BEN KHALFALLAH)</t>
+          <t xml:space="preserve">Kim (Imen AMERI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 17h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="D91">
         <is>
-          <t xml:space="preserve">R 11h-12h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E91">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">F 15h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I91">
@@ -4437,22 +4432,22 @@
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Laetitia (Amina BOUMAZA)</t>
+          <t xml:space="preserve">Kisha (Sondes AMARA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D92">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E92">
@@ -4462,17 +4457,17 @@
       </c>
       <c t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">V 14h-18h CH 14h-19h R 18h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="G92">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I92">
@@ -4484,42 +4479,42 @@
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Laura (Taheni MIZOUNI)</t>
+          <t xml:space="preserve">Kylian (Hassan BEN KHALFALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D93">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E93">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">R 16h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I93">
@@ -4531,32 +4526,32 @@
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Lea (Nadia BEN YOUNES)</t>
+          <t xml:space="preserve">Laetitia (Amina BOUMAZA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D94">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E94">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G94">
@@ -4571,190 +4566,190 @@
       </c>
       <c t="inlineStr" r="I94">
         <is>
-          <t xml:space="preserve">Formateur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Leah (Maram HIDRI)</t>
+          <t xml:space="preserve">Laura (Taheni MIZOUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D95">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E95">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I95">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Leto (Mongi BTACH)</t>
+          <t xml:space="preserve">Lea (Nadia BEN YOUNES)</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D96">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E96">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I96">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Formateur</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Liam (Iheb DOUCHEMEN)</t>
+          <t xml:space="preserve">Leah (Maram HIDRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D97">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E97">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G97">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I97">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Liana (Sarra KAMOUN)</t>
+          <t xml:space="preserve">Leto (Mongi BTACH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">14h-23h R 23h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">V 14h-18h R 18h-0h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="D98">
         <is>
-          <t xml:space="preserve">V 14h-18h R 18h-20h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="I98">
@@ -4766,42 +4761,42 @@
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Lilly (Ibtihel BEN KHALIFA)</t>
+          <t xml:space="preserve">Liam (Iheb DOUCHEMEN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D99">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I99">
@@ -4813,7 +4808,7 @@
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Lolita (Syrine BEN SBIHA)</t>
+          <t xml:space="preserve">Liana (Sarra KAMOUN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
@@ -4823,22 +4818,22 @@
       </c>
       <c t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D100">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E100">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G100">
@@ -4860,22 +4855,22 @@
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Ludmila  (Olfa ALLAYA)</t>
+          <t xml:space="preserve">Lilly (Ibtihel BEN KHALIFA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D101">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E101">
@@ -4890,39 +4885,39 @@
       </c>
       <c t="inlineStr" r="G101">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H101">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I101">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Luigy (Med taieb MANAI)</t>
+          <t xml:space="preserve">Lolita (Syrine BEN SBIHA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">F 16h-17h 18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">F 16h-17h 18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D102">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E102">
@@ -4937,12 +4932,12 @@
       </c>
       <c t="inlineStr" r="G102">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H102">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I102">
@@ -4954,79 +4949,79 @@
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Luna (Alyssa BEN ABDERRAZEK)</t>
+          <t xml:space="preserve">Ludmila  (Olfa ALLAYA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">17h-2h R 2h-3h R 3h-4h50</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D103">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E103">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G103">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H103">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I103">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Lyna (Lamia BRAHAM)</t>
+          <t xml:space="preserve">Luigy (Med taieb MANAI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 17h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">F 16h-17h 18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D104">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">F 16h-17h 18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E104">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G104">
@@ -5037,122 +5032,122 @@
       <c t="inlineStr" r="H104">
         <is>
           <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I104">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Mabrouka (Mabrouka HANZOULI)</t>
+          <t xml:space="preserve">Luna (Alyssa BEN ABDERRAZEK)</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D105">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E105">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G105">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I105">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Margot (Houda SELLAM)</t>
+          <t xml:space="preserve">Lyna (Lamia BRAHAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D106">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E106">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G106">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I106">
-        <is>
-          <t xml:space="preserve">Cadre</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Mary madison (Samia TAAMALLAH)</t>
+          <t xml:space="preserve">Mabrouka (Mabrouka HANZOULI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D107">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E107">
@@ -5162,59 +5157,59 @@
       </c>
       <c t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="G107">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I107">
         <is>
-          <t xml:space="preserve">Cadre</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Mathieu (Akram SBOUI)</t>
+          <t xml:space="preserve">Margot (Houda SELLAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D108">
         <is>
-          <t xml:space="preserve">11h-21h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E108">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G108">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H108">
@@ -5231,37 +5226,37 @@
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Maylie (Marwa DHOUIOUI)</t>
+          <t xml:space="preserve">Mary madison (Samia TAAMALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D109">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E109">
         <is>
-          <t xml:space="preserve">F 14h-15h 16h-1h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">F 14h-15h 16h-1h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G109">
         <is>
-          <t xml:space="preserve">R 20h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H109">
@@ -5271,96 +5266,96 @@
       </c>
       <c t="inlineStr" r="I109">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Cadre</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Mika (Omar SAIDANE)</t>
+          <t xml:space="preserve">Mathieu (Akram SBOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">R 17h-18h 18h-3h</t>
+          <t xml:space="preserve">9h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="D110">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">9h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="E110">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">9h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">9h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="G110">
         <is>
-          <t xml:space="preserve">R 20h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">R 20h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I110">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Cadre</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Miles (Ghaith AMRI)</t>
+          <t xml:space="preserve">Maylie (Marwa DHOUIOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C111">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D111">
+        <is>
+          <t xml:space="preserve">R 19h-21h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E111">
+        <is>
           <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D111">
+      <c t="inlineStr" r="F111">
         <is>
           <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E111">
+      <c t="inlineStr" r="G111">
         <is>
           <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F111">
+      <c t="inlineStr" r="H111">
         <is>
           <t xml:space="preserve">16h-1h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G111">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H111">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I111">
@@ -5372,42 +5367,42 @@
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Mirta (Sawssen AMMAR)</t>
+          <t xml:space="preserve">Mika (Omar SAIDANE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">R 11h-14h 16h-1h R 1h-2h R 2h-3h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">R 12h-15h 16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D112">
         <is>
-          <t xml:space="preserve">R 10h20-14h 17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E112">
         <is>
-          <t xml:space="preserve">R 10h-14h R 18h-0h</t>
+          <t xml:space="preserve">F 16h-17h 18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">R 10h-14h R 18h-0h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G112">
         <is>
-          <t xml:space="preserve">R 10h-14h 16h-1h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H112">
         <is>
-          <t xml:space="preserve">R 10h-14h 16h-1h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I112">
@@ -5419,69 +5414,69 @@
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Nahed (Nahed ZAGUIA)</t>
+          <t xml:space="preserve">Miles (Ghaith AMRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D113">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E113">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G113">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H113">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I113">
         <is>
-          <t xml:space="preserve">Comptable</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Naomi (Malek DHOUIHRI)</t>
+          <t xml:space="preserve">Mirta (Sawssen AMMAR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
+          <t xml:space="preserve">R 17h-23h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
           <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C114">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="D114">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E114">
@@ -5496,12 +5491,12 @@
       </c>
       <c t="inlineStr" r="G114">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H114">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I114">
@@ -5513,89 +5508,89 @@
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">Nesrine (Nesrine BEN KHALIFA)</t>
+          <t xml:space="preserve">Nahed (Nahed ZAGUIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="D115">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E115">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G115">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I115">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Comptable</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Nicolas (Med ali KTITA)</t>
+          <t xml:space="preserve">Naomi (Malek DHOUIHRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D116">
         <is>
-          <t xml:space="preserve">R 9h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E116">
         <is>
-          <t xml:space="preserve">9h-17h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">9h-17h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G116">
         <is>
-          <t xml:space="preserve">9h-17h30</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">9h-17h30</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I116">
@@ -5607,69 +5602,69 @@
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Nikki (Bochra BEN ROMDHANE)</t>
+          <t xml:space="preserve">Nesrine (Nesrine BEN KHALIFA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">R 15h-19h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D117">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E117">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G117">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="H117">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="I117">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Norbert (Nader CHADLI)</t>
+          <t xml:space="preserve">Nicolas (Med ali KTITA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D118">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E118">
@@ -5684,34 +5679,34 @@
       </c>
       <c t="inlineStr" r="G118">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I118">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Nourane (Saida KAROUI)</t>
+          <t xml:space="preserve">Nikki (Bochra BEN ROMDHANE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">F 14h-15h 15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 14h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D119">
@@ -5721,22 +5716,22 @@
       </c>
       <c t="inlineStr" r="E119">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">F 14h-15h 15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G119">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I119">
@@ -5748,27 +5743,27 @@
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Orianne (Meryam MOSREF)</t>
+          <t xml:space="preserve">Norbert (Nader CHADLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">R 12h-18h R 18h-23h R 23h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">9h-18h R 18h-20h R 20h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D120">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E120">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F120">
@@ -5778,39 +5773,39 @@
       </c>
       <c t="inlineStr" r="G120">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H120">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I120">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Oscar (Karim TRIFI)</t>
+          <t xml:space="preserve">Nourane (Saida KAROUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
+          <t xml:space="preserve">ABSENCE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
           <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C121">
+      <c t="inlineStr" r="D121">
         <is>
           <t xml:space="preserve">13h-22h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D121">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E121">
@@ -5842,79 +5837,79 @@
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Oussema (Oussama ELKHARAT)</t>
+          <t xml:space="preserve">Orianne (Meryam MOSREF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H122">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I122">
         <is>
-          <t xml:space="preserve">Dirigeant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">Pablo (Becheur BOURAOUI)</t>
+          <t xml:space="preserve">Oscar (Karim TRIFI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">14h-23h R 23h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D123">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E123">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G123">
@@ -5936,89 +5931,89 @@
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Paolo (Mohamed hedi MARRAKCHI)</t>
+          <t xml:space="preserve">Oussema (Oussama ELKHARAT)</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="D124">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="E124">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="G124">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="H124">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="I124">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Dirigeant</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">Percey (Ahmed CHAABENI)</t>
+          <t xml:space="preserve">Pablo (Becheur BOURAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">F 13h-14h 14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">R 21h-3h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H125">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I125">
@@ -6030,89 +6025,89 @@
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Petra (Halima MADHBOUH)</t>
+          <t xml:space="preserve">Paolo (Mohamed hedi MARRAKCHI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">16h-1h R 1h-2h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D126">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E126">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G126">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H126">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I126">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">Ramon (Khaled RAHMANI)</t>
+          <t xml:space="preserve">Percey (Ahmed CHAABENI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h R+ 0h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D127">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E127">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G127">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H127">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I127">
@@ -6124,89 +6119,89 @@
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">Raven (Asma HAMROUNI)</t>
+          <t xml:space="preserve">Petra (Halima MADHBOUH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D128">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E128">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G128">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H128">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I128">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Reine (Jihen GUESMI)</t>
+          <t xml:space="preserve">Ramon (Khaled RAHMANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h P 16h50-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H129">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I129">
@@ -6218,32 +6213,32 @@
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">Reza (Safa RAGGUEM)</t>
+          <t xml:space="preserve">Raven (Asma HAMROUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">R 19h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">13h-22h R 22h-0h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D130">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E130">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G130">
@@ -6253,54 +6248,54 @@
       </c>
       <c t="inlineStr" r="H130">
         <is>
-          <t xml:space="preserve">R+ 14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I130">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">Rick (Souhail GASMIA)</t>
+          <t xml:space="preserve">Reine (Jihen GUESMI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CH 18h-0h R 18h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D131">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CH 18h-0h R 18h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E131">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G131">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H131">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I131">
@@ -6312,42 +6307,42 @@
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Rubi (Nour REZGUI)</t>
+          <t xml:space="preserve">Reza (Safa RAGGUEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">R 22h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D132">
         <is>
-          <t xml:space="preserve">19h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E132">
         <is>
-          <t xml:space="preserve">19h-2h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">19h-2h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G132">
         <is>
-          <t xml:space="preserve">19h-2h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H132">
         <is>
-          <t xml:space="preserve">19h-2h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I132">
@@ -6359,32 +6354,32 @@
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Sahar (Sahar FEKIH)</t>
+          <t xml:space="preserve">Rick (Souhail GASMIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D133">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E133">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G133">
@@ -6399,24 +6394,24 @@
       </c>
       <c t="inlineStr" r="I133">
         <is>
-          <t xml:space="preserve">Comptable</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Salvadore (Omar RIDEN)</t>
+          <t xml:space="preserve">Rubi (Nour REZGUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">16h-1h R 1h-2h</t>
+          <t xml:space="preserve">23h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">16h-1h R 1h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D134">
@@ -6426,22 +6421,22 @@
       </c>
       <c t="inlineStr" r="E134">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="G134">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="H134">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">23h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="I134">
@@ -6453,32 +6448,32 @@
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Sia (Cyrine BEN CHEIKH MOHAMED)</t>
+          <t xml:space="preserve">Sahar (Sahar FEKIH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D135">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E135">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G135">
@@ -6488,54 +6483,54 @@
       </c>
       <c t="inlineStr" r="H135">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I135">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Comptable</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Silas (Hamdi GHARRAD)</t>
+          <t xml:space="preserve">Salvadore (Omar RIDEN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">F 15h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D136">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E136">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G136">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H136">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I136">
@@ -6547,7 +6542,7 @@
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Simone (Lamia BRAHAM)</t>
+          <t xml:space="preserve">Sia (Cyrine BEN CHEIKH MOHAMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
@@ -6557,27 +6552,27 @@
       </c>
       <c t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D137">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="E137">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="G137">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H137">
@@ -6587,108 +6582,113 @@
       </c>
       <c t="inlineStr" r="I137">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Stacey (Rania GRABA)</t>
+          <t xml:space="preserve">Silas (Hamdi GHARRAD)</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D138">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E138">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G138">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H138">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I138">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Stella (Nahla AYADI)</t>
+          <t xml:space="preserve">Simone (Lamia BRAHAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D139">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E139">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G139">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="H139">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I139">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Steve (Seif BEN CHEIKH MOHAMED)</t>
+          <t xml:space="preserve">Stacey (Rania GRABA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C140">
@@ -6703,116 +6703,111 @@
       </c>
       <c t="inlineStr" r="E140">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G140">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H140">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I140">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Suzy (Fatma GHEDIRA)</t>
+          <t xml:space="preserve">Stella (Nahla AYADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">9h-16h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">8h-15h R 15h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D141">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E141">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="G141">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="H141">
         <is>
-          <t xml:space="preserve">8h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I141">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Sylvia (Souha MISSAOUI)</t>
+          <t xml:space="preserve">Steve (Seif BEN CHEIKH MOHAMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="D142">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="E142">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G142">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="H142">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="I142">
@@ -6824,42 +6819,42 @@
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Theresa (Wafa OUESLETI)</t>
+          <t xml:space="preserve">Suzy (Fatma GHEDIRA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">R 20h15-22h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D143">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E143">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G143">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H143">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I143">
@@ -6871,54 +6866,54 @@
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Tobias (Slim YAHYAOUI)</t>
+          <t xml:space="preserve">Sylvia (Souha MISSAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D144">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E144">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">R+ 15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G144">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H144">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I144">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Tommy (Nizar SOUILEM)</t>
+          <t xml:space="preserve">Theresa (Wafa OUESLETI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
@@ -6965,12 +6960,12 @@
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Tony (Nabil MANSOURI)</t>
+          <t xml:space="preserve">Tobias (Slim YAHYAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C146">
@@ -6995,59 +6990,59 @@
       </c>
       <c t="inlineStr" r="G146">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H146">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I146">
         <is>
-          <t xml:space="preserve">Rédacteur mail</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Tova (Asma CHOUCHENE)</t>
+          <t xml:space="preserve">Tommy (Nizar SOUILEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D147">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E147">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G147">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H147">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I147">
@@ -7059,12 +7054,12 @@
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Travis (Mohamed BEN HFAIEDH)</t>
+          <t xml:space="preserve">Tony (Nabil MANSOURI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C148">
@@ -7079,69 +7074,69 @@
       </c>
       <c t="inlineStr" r="E148">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G148">
         <is>
-          <t xml:space="preserve">R 15h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H148">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I148">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Rédacteur mail</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Troy (Ala BOUZID)</t>
+          <t xml:space="preserve">Tova (Asma CHOUCHENE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D149">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E149">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G149">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="H149">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I149">
@@ -7153,42 +7148,42 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Ursula (Najia anouar DERBEZ)</t>
+          <t xml:space="preserve">Travis (Mohamed BEN HFAIEDH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">5h-14h CH 18h-21h R 18h-21h</t>
+          <t xml:space="preserve">F 14h-15h 15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D150">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E150">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">F 14h-15h 15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G150">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H150">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I150">
@@ -7200,42 +7195,42 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Vanessa (Olfa CHOUAIEB)</t>
+          <t xml:space="preserve">Troy (Ala BOUZID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">R 21h-1h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D151">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E151">
         <is>
-          <t xml:space="preserve">15h-0h P 17h30-19h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G151">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H151">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I151">
@@ -7247,42 +7242,42 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Vladimir (Nessim HAJJI)</t>
+          <t xml:space="preserve">Ursula (Najia anouar DERBEZ)</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">R 5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="D152">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="E152">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="G152">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H152">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I152">
@@ -7294,74 +7289,79 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Voy_test_deux (Voy PRODTEST)</t>
+          <t xml:space="preserve">Vanessa (Olfa CHOUAIEB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D153">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E153">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F153">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G153">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H153">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I153">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Voy_test_trois (Voy PRODTEST)</t>
+          <t xml:space="preserve">Vladimir (Nessim HAJJI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D154">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E154">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G154">
@@ -7383,79 +7383,74 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Whitney (Ghofran NASRALLI)</t>
+          <t xml:space="preserve">Voy_test_deux (Voy PRODTEST)</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h R 22h-23h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">14h-23h CH 14h-23h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D155">
         <is>
-          <t xml:space="preserve">15h-0h CH 15h-0h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E155">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G155">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H155">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I155">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Yadira (Mayssa KAROUI)</t>
+          <t xml:space="preserve">Voy_test_trois (Voy PRODTEST)</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D156">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E156">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G156">
@@ -7477,17 +7472,17 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Yann (Mhamed KEDADI)</t>
+          <t xml:space="preserve">Wafa (Wafa HICHRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D157">
@@ -7517,39 +7512,39 @@
       </c>
       <c t="inlineStr" r="I157">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Chargé de recrutement</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Yasser (Yesser NCIR)</t>
+          <t xml:space="preserve">Whitney (Ghofran NASRALLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">9h30-18h30</t>
+          <t xml:space="preserve">CH 15h15-21h15 R 15h15-21h15</t>
         </is>
       </c>
       <c t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">9h30-18h30</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D158">
         <is>
-          <t xml:space="preserve">9h30-18h30</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E158">
         <is>
-          <t xml:space="preserve">9h30-18h30</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">9h30-18h30</t>
+          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G158">
@@ -7564,49 +7559,49 @@
       </c>
       <c t="inlineStr" r="I158">
         <is>
-          <t xml:space="preserve">Technicien</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Zayn (Hamza BOUALLEGUE)</t>
+          <t xml:space="preserve">Yadira (Mayssa KAROUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D159">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E159">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G159">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I159">
@@ -7618,45 +7613,186 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
+          <t xml:space="preserve">Yann (Mhamed KEDADI)</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D160">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E160">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F160">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G160">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H160">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I160">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c t="inlineStr" r="A161">
+        <is>
+          <t xml:space="preserve">Yasser (Yesser NCIR)</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">9h30-18h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">9h30-18h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D161">
+        <is>
+          <t xml:space="preserve">9h30-18h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E161">
+        <is>
+          <t xml:space="preserve">9h30-18h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F161">
+        <is>
+          <t xml:space="preserve">9h30-18h30</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G161">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H161">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I161">
+        <is>
+          <t xml:space="preserve">Technicien</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c t="inlineStr" r="A162">
+        <is>
+          <t xml:space="preserve">Zayn (Hamza BOUALLEGUE)</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D162">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E162">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F162">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G162">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H162">
+        <is>
+          <t xml:space="preserve">15h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I162">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c t="inlineStr" r="A163">
+        <is>
           <t xml:space="preserve">Zen (Bahaa eddine BELHOUCHE)</t>
         </is>
       </c>
-      <c t="inlineStr" r="B160">
+      <c t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C163">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C160">
+      <c t="inlineStr" r="D163">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D160">
+      <c t="inlineStr" r="E163">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E160">
-        <is>
-          <t xml:space="preserve">R 6h-11h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F160">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G160">
+      <c t="inlineStr" r="F163">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="H160">
-        <is>
-          <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I160">
+      <c t="inlineStr" r="G163">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H163">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I163">
         <is>
           <t xml:space="preserve">Téléconseiller</t>
         </is>

--- a/media/temp_planning.xlsx
+++ b/media/temp_planning.xlsx
@@ -203,10 +203,10 @@
   <cols>
     <col min="1" max="1" width="44.550000000000004" customWidth="1"/>
     <col min="2" max="2" width="47.25" customWidth="1"/>
-    <col min="3" max="3" width="24.3" customWidth="1"/>
+    <col min="3" max="3" width="47.25" customWidth="1"/>
     <col min="4" max="4" width="24.3" customWidth="1"/>
     <col min="5" max="5" width="24.3" customWidth="1"/>
-    <col min="6" max="6" width="40.5" customWidth="1"/>
+    <col min="6" max="6" width="24.3" customWidth="1"/>
     <col min="7" max="7" width="24.3" customWidth="1"/>
     <col min="8" max="8" width="24.3" customWidth="1"/>
     <col min="9" max="9" width="40.5" customWidth="1"/>
@@ -227,37 +227,37 @@
       </c>
       <c t="inlineStr" r="B2" s="2">
         <is>
-          <t xml:space="preserve">Lundi  2/02</t>
+          <t xml:space="preserve">Lundi 23/02</t>
         </is>
       </c>
       <c t="inlineStr" r="C2" s="2">
         <is>
-          <t xml:space="preserve">Mardi  3/02</t>
+          <t xml:space="preserve">Mardi 24/02</t>
         </is>
       </c>
       <c t="inlineStr" r="D2" s="2">
         <is>
-          <t xml:space="preserve">Mercredi  4/02</t>
+          <t xml:space="preserve">Mercredi 25/02</t>
         </is>
       </c>
       <c t="inlineStr" r="E2" s="2">
         <is>
-          <t xml:space="preserve">Jeudi  5/02</t>
+          <t xml:space="preserve">Jeudi 26/02</t>
         </is>
       </c>
       <c t="inlineStr" r="F2" s="2">
         <is>
-          <t xml:space="preserve">Vendredi  6/02</t>
+          <t xml:space="preserve">Vendredi 27/02</t>
         </is>
       </c>
       <c t="inlineStr" r="G2" s="2">
         <is>
-          <t xml:space="preserve">Samedi  7/02</t>
+          <t xml:space="preserve">Samedi 28/02</t>
         </is>
       </c>
       <c t="inlineStr" r="H2" s="2">
         <is>
-          <t xml:space="preserve">Dimanche  8/02</t>
+          <t xml:space="preserve">Dimanche  1/03</t>
         </is>
       </c>
       <c t="inlineStr" r="I2" s="2">
@@ -274,27 +274,27 @@
       </c>
       <c t="inlineStr" r="B3">
         <is>
-          <t xml:space="preserve">8h-16h R 16h-19h</t>
+          <t xml:space="preserve">R 12h35-16h35</t>
         </is>
       </c>
       <c t="inlineStr" r="C3">
         <is>
+          <t xml:space="preserve">R 12h15-16h15</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D3">
+        <is>
           <t xml:space="preserve">8h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D3">
+      <c t="inlineStr" r="E3">
         <is>
           <t xml:space="preserve">8h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E3">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
@@ -304,7 +304,7 @@
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">8h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
@@ -321,29 +321,29 @@
       </c>
       <c t="inlineStr" r="B4">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C4">
+        <is>
+          <t xml:space="preserve">CH 14h-0h R 14h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D4">
+        <is>
           <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C4">
+      <c t="inlineStr" r="E4">
         <is>
           <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D4">
+      <c t="inlineStr" r="F4">
         <is>
           <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E4">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F4">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="G4">
         <is>
           <t xml:space="preserve">13h-22h</t>
@@ -351,7 +351,7 @@
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
@@ -415,27 +415,27 @@
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="D6">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
@@ -462,37 +462,37 @@
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">MISE À PIED</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D7">
         <is>
-          <t xml:space="preserve">MISE À PIED</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E7">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F7">
+        <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F7">
+      <c t="inlineStr" r="G7">
         <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="G7">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
@@ -509,29 +509,29 @@
       </c>
       <c t="inlineStr" r="B8">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C8">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D8">
+        <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C8">
+      <c t="inlineStr" r="E8">
         <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D8">
+      <c t="inlineStr" r="F8">
         <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E8">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F8">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="G8">
         <is>
           <t xml:space="preserve">12h-21h</t>
@@ -539,7 +539,7 @@
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
@@ -561,12 +561,12 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D9">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E9">
@@ -576,12 +576,12 @@
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
@@ -603,7 +603,7 @@
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
@@ -613,27 +613,27 @@
       </c>
       <c t="inlineStr" r="D10">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E10">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F10">
+        <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E10">
+      <c t="inlineStr" r="G10">
         <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F10">
+      <c t="inlineStr" r="H10">
         <is>
           <t xml:space="preserve">14h-23h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G10">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H10">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
@@ -650,32 +650,32 @@
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">21h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">21h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D11">
         <is>
-          <t xml:space="preserve">21h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">21h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">21h-2h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
@@ -692,37 +692,37 @@
       </c>
       <c t="inlineStr" r="B12">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C12">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D12">
+        <is>
           <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C12">
+      <c t="inlineStr" r="E12">
+        <is>
+          <t xml:space="preserve">6h-16h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F12">
         <is>
           <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D12">
+      <c t="inlineStr" r="G12">
         <is>
           <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E12">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F12">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G12">
-        <is>
-          <t xml:space="preserve">6h-16h</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
@@ -739,37 +739,37 @@
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-2h R 2h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D13">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
@@ -786,37 +786,37 @@
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="D14">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
@@ -833,17 +833,17 @@
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">5h-14h CH 16h10-18h10 R 16h10-18h10</t>
+          <t xml:space="preserve">5h-14h CH 15h15-17h15 R 15h15-17h15</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">CH 5h-12h R 5h-12h</t>
+          <t xml:space="preserve">5h-14h CH 15h20-17h20 R 15h20-17h20</t>
         </is>
       </c>
       <c t="inlineStr" r="D15">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="E15">
@@ -853,12 +853,12 @@
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
@@ -880,37 +880,37 @@
       </c>
       <c t="inlineStr" r="B16">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D16">
+        <is>
           <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C16">
+      <c t="inlineStr" r="E16">
+        <is>
+          <t xml:space="preserve">7h-16h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F16">
         <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D16">
+      <c t="inlineStr" r="G16">
         <is>
           <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E16">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F16">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G16">
-        <is>
-          <t xml:space="preserve">7h-16h</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
@@ -927,29 +927,29 @@
       </c>
       <c t="inlineStr" r="B17">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">CH 20h-1h R 20h-1h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D17">
+        <is>
           <t xml:space="preserve">16h-1h CH 17h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C17">
+      <c t="inlineStr" r="E17">
         <is>
           <t xml:space="preserve">16h-1h CH 17h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D17">
+      <c t="inlineStr" r="F17">
         <is>
           <t xml:space="preserve">16h-1h CH 17h-1h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E17">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F17">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="G17">
         <is>
           <t xml:space="preserve">16h-1h CH 17h-1h</t>
@@ -957,7 +957,7 @@
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">16h-1h CH 17h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I17">
@@ -979,27 +979,27 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D18">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 7h-11h</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
@@ -1120,12 +1120,12 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D21">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E21">
@@ -1135,12 +1135,12 @@
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
@@ -1157,32 +1157,32 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Aziz (Abdelaziz bilel BRAHAM)</t>
+          <t xml:space="preserve">Bayram (Bayrem SAYEH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-4h</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">19h-4h</t>
         </is>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">19h-4h</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">19h-4h</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">19h-4h</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
@@ -1197,44 +1197,44 @@
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Technicien</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Bayram (Bayrem SAYEH)</t>
+          <t xml:space="preserve">Betty (Soulef BEN AMOR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">R 7h-10h</t>
         </is>
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
@@ -1244,34 +1244,34 @@
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">Technicien</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">Betty (Soulef BEN AMOR)</t>
+          <t xml:space="preserve">Brann (Marwen HOSNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">14h-23h R 23h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
@@ -1281,12 +1281,12 @@
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
@@ -1298,42 +1298,42 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">Brann (Marwen HOSNI)</t>
+          <t xml:space="preserve">Briana (Latifa BEN MANSOUR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D25">
         <is>
-          <t xml:space="preserve">V 14h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
@@ -1345,32 +1345,32 @@
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">Briana (Latifa BEN MANSOUR)</t>
+          <t xml:space="preserve">Britney (Wided LAAROUSSI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">CH 16h-22h R 16h-22h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="D26">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
@@ -1380,39 +1380,34 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I26">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">0h-6h</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">Britney (Wided LAAROUSSI)</t>
+          <t xml:space="preserve">Brooklyn (Soumaya ZAALOUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D27">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1422,34 +1417,39 @@
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">0h-6h</t>
+          <t xml:space="preserve">14h-0h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I27">
+        <is>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">Brooklyn (Soumaya ZAALOUNI)</t>
+          <t xml:space="preserve">Bruce (Kacem ROMDHANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D28">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E28">
@@ -1459,59 +1459,59 @@
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Bruce (Kacem ROMDHANI)</t>
+          <t xml:space="preserve">Carla (Saida ABDELLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 20h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D29">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h-17h R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
@@ -1521,49 +1521,49 @@
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">Carla (Saida ABDELLI)</t>
+          <t xml:space="preserve">Cedric (Amine ASKRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D30">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
@@ -1575,42 +1575,42 @@
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">Cedric (Amine ASKRI)</t>
+          <t xml:space="preserve">Cersei (Khaoula BRAHIM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 19h-4h50</t>
         </is>
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 20h-4h50</t>
         </is>
       </c>
       <c t="inlineStr" r="D31">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
@@ -1622,165 +1622,165 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">Cersei (Khaoula BRAHIM)</t>
+          <t xml:space="preserve">Cesar (Mohamed BOUCHIBA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">Cesar (Mohamed BOUCHIBA)</t>
+          <t xml:space="preserve">Chafika (Chafika CHAOUECH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="D33">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">Chafika (Chafika CHAOUECH)</t>
+          <t xml:space="preserve">Chloe (Jihene BOUSLAMA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D34">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">R 19h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Chloe (Jihene BOUSLAMA)</t>
+          <t xml:space="preserve">Colin (Marwen BAGHDADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">R 16h-18h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D35">
+        <is>
           <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C35">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D35">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="E35">
         <is>
           <t xml:space="preserve">15h-0h</t>
@@ -1798,7 +1798,7 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
@@ -1810,96 +1810,96 @@
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">Colin (Marwen BAGHDADI)</t>
+          <t xml:space="preserve">Collins (Lotfi BOUDHIB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D36">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">19h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I36">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">Collins (Lotfi BOUDHIB)</t>
+          <t xml:space="preserve">Cora (Manel GAFSAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D37">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">19h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I37">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">Cora (Manel GAFSAOUI)</t>
+          <t xml:space="preserve">Damen (Nour CHELLY)</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
@@ -1909,27 +1909,27 @@
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D38">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
@@ -1939,29 +1939,29 @@
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">Damen (Nour CHELLY)</t>
+          <t xml:space="preserve">Damien (Hatem BEN ZINEB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D39">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E39">
@@ -1971,29 +1971,29 @@
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">R 16h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">Damien (Hatem BEN ZINEB)</t>
+          <t xml:space="preserve">Darius (Mejdi EL AYED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
@@ -2003,27 +2003,27 @@
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 10h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D40">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
@@ -2040,7 +2040,7 @@
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Darius (Mejdi EL AYED)</t>
+          <t xml:space="preserve">Davina (Arwa JOUBID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
@@ -2055,17 +2055,17 @@
       </c>
       <c t="inlineStr" r="D41">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E41">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F41">
+        <is>
           <t xml:space="preserve">9h-18h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E41">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F41">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G41">
@@ -2087,42 +2087,42 @@
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Davina (Arwa JOUBID)</t>
+          <t xml:space="preserve">Deborah (Najla AHMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D42">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I42">
@@ -2134,17 +2134,17 @@
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">Deborah (Najla AHMED)</t>
+          <t xml:space="preserve">Diane (Radhia CHAKROUN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">8h-15h F 15h-16h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D43">
@@ -2154,22 +2154,22 @@
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">8h-15h F 15h-16h</t>
+          <t xml:space="preserve">R 18h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
@@ -2181,17 +2181,17 @@
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">Diane (Radhia CHAKROUN)</t>
+          <t xml:space="preserve">Donis (Houcem EL GHOUL)</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">R 19h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">F 13h-14h 14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D44">
@@ -2211,7 +2211,7 @@
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
@@ -2228,22 +2228,22 @@
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">Donis (Houcem EL GHOUL)</t>
+          <t xml:space="preserve">Doris (Rihab SGHAIR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D45">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E45">
@@ -2253,17 +2253,17 @@
       </c>
       <c t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
@@ -2275,42 +2275,42 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Doris (Rihab SGHAIR)</t>
+          <t xml:space="preserve">Dustin (Faeez HENI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D46">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
@@ -2322,17 +2322,17 @@
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Drake (Mohamed bechir BEZI)</t>
+          <t xml:space="preserve">Eddy (Hamdi CHERIF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D47">
@@ -2342,54 +2342,59 @@
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">15h-19h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">15h-19h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">15h-19h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">15h-19h</t>
+          <t xml:space="preserve">17h-2h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I47">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Dustin (Faeez HENI)</t>
+          <t xml:space="preserve">Elena (Ines CHOUCHANNE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D48">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
@@ -2399,7 +2404,7 @@
       </c>
       <c t="inlineStr" r="H48">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="I48">
@@ -2411,37 +2416,37 @@
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Eddy (Hamdi CHERIF)</t>
+          <t xml:space="preserve">Emile (Franck roland danie N'DRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">R 10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">R 11h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="D49">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
@@ -2458,89 +2463,89 @@
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Elena (Ines CHOUCHANNE)</t>
+          <t xml:space="preserve">Emilio (Ahmed HOURY)</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D50">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Formateur</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Emile (Franck roland danie N'DRI)</t>
+          <t xml:space="preserve">Enola (Khouloud FARJALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D51">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
@@ -2552,89 +2557,89 @@
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Emilio (Ahmed HOURY)</t>
+          <t xml:space="preserve">Esther (Amal GALBI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">10h-19h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">10h-19h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D52">
         <is>
-          <t xml:space="preserve">10h-19h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">10h-19h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
         <is>
-          <t xml:space="preserve">10h-19h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">Formateur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Enola (Khouloud FARJALLAH)</t>
+          <t xml:space="preserve">Evan (Rochdi LARIBI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D53">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">R 15h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
@@ -2646,89 +2651,89 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Esther (Amal GALBI)</t>
+          <t xml:space="preserve">Eve (Ons BEN AMOR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D54">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Evan (Rochdi LARIBI)</t>
+          <t xml:space="preserve">Evita (Imen NASRAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="D55">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
@@ -2740,89 +2745,89 @@
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Eve (Ons BEN AMOR)</t>
+          <t xml:space="preserve">Fabrice (Mohamed ridha FRADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D56">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">14h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Evita (Imen NASRAOUI)</t>
+          <t xml:space="preserve">Felix (Mohamed MANSOURI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h R 1h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
@@ -2834,22 +2839,22 @@
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Fabrice (Mohamed ridha FRADI)</t>
+          <t xml:space="preserve">Feriel (Feriel SGHAIER)</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">8h-17h R 19h-21h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D58">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="E58">
@@ -2864,96 +2869,96 @@
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Auditeur</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Felix (Mohamed MANSOURI)</t>
+          <t xml:space="preserve">Fiona (Faieza ESSID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">R 17h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D59">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Feriel (Feriel SGHAIER)</t>
+          <t xml:space="preserve">Galia (Nahla AYADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">12h-21h CH 21h-23h R 21h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="D60">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G60">
@@ -2963,39 +2968,39 @@
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">Auditeur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Fiona (Faieza ESSID)</t>
+          <t xml:space="preserve">Gwen (Ghalia FRAJ)</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">R 22h-23h 23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="D61">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
@@ -3005,12 +3010,12 @@
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-8h</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
@@ -3022,17 +3027,17 @@
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Galia (Nahla AYADI)</t>
+          <t xml:space="preserve">Hannah (Hanedi NASR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D62">
@@ -3042,106 +3047,106 @@
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Auditeur</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Gwen (Ghalia FRAJ)</t>
+          <t xml:space="preserve">Harry (Mohamed nacer JDIDI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">V 17h-18h 18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">V 17h-18h 18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D63">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G63">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Hannah (Hanedi NASR)</t>
+          <t xml:space="preserve">Holly (Khouloud ZAMMEL)</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h R 2h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D64">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
@@ -3151,24 +3156,24 @@
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">Auditeur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Harry (Mohamed nacer JDIDI)</t>
+          <t xml:space="preserve">Ilhem  (Ilhem FAIECH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C65">
@@ -3178,74 +3183,74 @@
       </c>
       <c t="inlineStr" r="D65">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Holly (Khouloud ZAMMEL)</t>
+          <t xml:space="preserve">Imane (Imen HANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D66">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">9h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
@@ -3257,79 +3262,79 @@
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Ilhem  (Ilhem FAIECH)</t>
+          <t xml:space="preserve">Iris (Amal FRADI NÉE DARDOUR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D67">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">R 9h-12h</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Imane (Imen HANI)</t>
+          <t xml:space="preserve">Irma (Insaf LETAIEF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D68">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E68">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t xml:space="preserve">9h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
@@ -3339,7 +3344,7 @@
       </c>
       <c t="inlineStr" r="H68">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I68">
@@ -3351,101 +3356,101 @@
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Iris (Amal FRADI NÉE DARDOUR)</t>
+          <t xml:space="preserve">Isaac (Salem BEN SLAMA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">8h-17h R 19h-21h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">R 19h-21h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D69">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E69">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Créateur de contenu multimédia</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Irma (Insaf LETAIEF)</t>
+          <t xml:space="preserve">Isacc (Anis MOKNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="D70">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="E70">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G70">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Isaac (Salem BEN SLAMA)</t>
+          <t xml:space="preserve">Jade (Ouejdene OUERGHI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
@@ -3455,27 +3460,27 @@
       </c>
       <c t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D71">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E71">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F71">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">22h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="G71">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">22h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="H71">
@@ -3485,19 +3490,19 @@
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t xml:space="preserve">Créateur de contenu multimédia</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Isacc (Anis MOKNI)</t>
+          <t xml:space="preserve">Jaime (Achref MLOUKA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">V 14h-18h R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="C72">
@@ -3507,54 +3512,54 @@
       </c>
       <c t="inlineStr" r="D72">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G72">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Jade (Ouejdene OUERGHI)</t>
+          <t xml:space="preserve">Jairo (Mohamed KHAIR EDDINE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D73">
         <is>
-          <t xml:space="preserve">23h-8h</t>
+          <t xml:space="preserve">R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="E73">
@@ -3564,64 +3569,64 @@
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">Jaime (Achref MLOUKA)</t>
+          <t xml:space="preserve">James (Anouar ATTIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 14h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 14h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D74">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 14h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="E74">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 14h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 14h-17h 17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
@@ -3633,32 +3638,32 @@
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">Jairo (Mohamed KHAIR EDDINE)</t>
+          <t xml:space="preserve">Jamila  (Jamila HANZOULI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">F 15h-16h 16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D75">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E75">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G75">
@@ -3668,49 +3673,49 @@
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">James (Anouar ATTIA)</t>
+          <t xml:space="preserve">Javier (Mohamed iheb ASKRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">F 13h-14h R 14h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D76">
         <is>
-          <t xml:space="preserve">F 16h-17h 17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">F 16h-17h 17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
@@ -3727,89 +3732,89 @@
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Jamila  (Jamila HANZOULI)</t>
+          <t xml:space="preserve">Joaquin (Nassim BEN AZIZA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C77">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D77">
+        <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D77">
+      <c t="inlineStr" r="E77">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E77">
+      <c t="inlineStr" r="F77">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="F77">
+      <c t="inlineStr" r="G77">
         <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="G77">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Javier (Mohamed iheb ASKRI)</t>
+          <t xml:space="preserve">Jocelyne (Soraya AISSA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">R 20h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D78">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-13h 19h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E78">
         <is>
-          <t xml:space="preserve">F 16h-17h</t>
+          <t xml:space="preserve">7h-13h 19h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-13h 19h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G78">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-13h 19h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I78">
@@ -3821,7 +3826,7 @@
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Joaquin (Nassim BEN AZIZA)</t>
+          <t xml:space="preserve">John (Mohamed MOKNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
@@ -3836,17 +3841,17 @@
       </c>
       <c t="inlineStr" r="D79">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E79">
+        <is>
+          <t xml:space="preserve">R 6h30-12h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F79">
+        <is>
           <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E79">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F79">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G79">
@@ -3868,42 +3873,42 @@
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">Jocelyne (Soraya AISSA)</t>
+          <t xml:space="preserve">Jolaine (Amira AOUINA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="D80">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="E80">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="G80">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">MALADIE</t>
         </is>
       </c>
       <c t="inlineStr" r="I80">
@@ -3915,37 +3920,37 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">John (Mohamed MOKNI)</t>
+          <t xml:space="preserve">Jonas (Younes GHABRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 22h-1h30</t>
         </is>
       </c>
       <c t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D81">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E81">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G81">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H81">
@@ -3962,42 +3967,42 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Jolaine (Amira AOUINA)</t>
+          <t xml:space="preserve">Jules (Hefdhi BRAHEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">14h-23h CH 14h-23h R 23h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">CH 14h-23h 14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H82">
         <is>
-          <t xml:space="preserve">MALADIE</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I82">
@@ -4009,42 +4014,42 @@
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Jonas (Younes GHABRI)</t>
+          <t xml:space="preserve">Julienne (Samia HAMROUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">R 15h-16h 16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D83">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="E83">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="I83">
@@ -4056,126 +4061,126 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Jules (Hefdhi BRAHEM)</t>
+          <t xml:space="preserve">Kamilla (Khadija SOUISSI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="D84">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E84">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="I84">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Julienne (Samia HAMROUNI)</t>
+          <t xml:space="preserve">Karim (Karim SELLAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">9h30-18h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">9h30-18h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I85">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Technicien</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Kamilla (Khadija SOUISSI)</t>
+          <t xml:space="preserve">Karl (Nour elyakin MBARKI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D86">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E86">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G86">
@@ -4185,44 +4190,44 @@
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I86">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Karim (Karim SELLAM)</t>
+          <t xml:space="preserve">Kayn (Tarek JLASSI MONASTIRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D87">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E87">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G87">
@@ -4232,54 +4237,54 @@
       </c>
       <c t="inlineStr" r="H87">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I87">
         <is>
-          <t xml:space="preserve">Technicien</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Karl (Nour elyakin MBARKI)</t>
+          <t xml:space="preserve">Kenzo (Mohamed khairi MRIZAK)</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D88">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E88">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G88">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H88">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I88">
@@ -4291,89 +4296,89 @@
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Kayn (Tarek JLASSI MONASTIRI)</t>
+          <t xml:space="preserve">Kim (Imen AMERI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D89">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E89">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G89">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="I89">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Kenzo (Mohamed khairi MRIZAK)</t>
+          <t xml:space="preserve">Kisha (Sondes AMARA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CH 14h-20h V 14h-18h R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="D90">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E90">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I90">
@@ -4385,42 +4390,42 @@
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Kim (Imen AMERI)</t>
+          <t xml:space="preserve">Kylian (Hassan BEN KHALFALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">R 17h-19h</t>
+          <t xml:space="preserve">R 12h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="D91">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E91">
         <is>
-          <t xml:space="preserve">F 15h-16h 16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I91">
@@ -4432,22 +4437,22 @@
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Kisha (Sondes AMARA)</t>
+          <t xml:space="preserve">Laetitia (Amina BOUMAZA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D92">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E92">
@@ -4457,17 +4462,17 @@
       </c>
       <c t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">V 14h-18h CH 14h-19h R 18h-19h</t>
+          <t xml:space="preserve">7h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G92">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">7h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">7h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I92">
@@ -4479,42 +4484,42 @@
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Kylian (Hassan BEN KHALFALLAH)</t>
+          <t xml:space="preserve">Laura (Taheni MIZOUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 17h05-21h05</t>
         </is>
       </c>
       <c t="inlineStr" r="D93">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E93">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">R 16h-20h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I93">
@@ -4526,32 +4531,32 @@
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Laetitia (Amina BOUMAZA)</t>
+          <t xml:space="preserve">Lea (Nadia BEN YOUNES)</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D94">
         <is>
-          <t xml:space="preserve">7h-15h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E94">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G94">
@@ -4566,118 +4571,118 @@
       </c>
       <c t="inlineStr" r="I94">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Formateur</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Laura (Taheni MIZOUNI)</t>
+          <t xml:space="preserve">Leah (Maram HIDRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="D95">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="E95">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">CONGÉ PAYÉ</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I95">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Lea (Nadia BEN YOUNES)</t>
+          <t xml:space="preserve">Leto (Mongi BTACH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D96">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E96">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I96">
         <is>
-          <t xml:space="preserve">Formateur</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Leah (Maram HIDRI)</t>
+          <t xml:space="preserve">Liam (Iheb DOUCHEMEN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="D97">
@@ -4687,69 +4692,69 @@
       </c>
       <c t="inlineStr" r="E97">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G97">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="I97">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Leto (Mongi BTACH)</t>
+          <t xml:space="preserve">Liana (Sarra KAMOUN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">V 14h-18h R 18h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">V 14h-18h R 18h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="D98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I98">
@@ -4761,7 +4766,7 @@
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Liam (Iheb DOUCHEMEN)</t>
+          <t xml:space="preserve">Lilly (Ibtihel BEN KHALIFA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
@@ -4771,27 +4776,27 @@
       </c>
       <c t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 19h30-22h30</t>
         </is>
       </c>
       <c t="inlineStr" r="D99">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
@@ -4808,34 +4813,34 @@
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Liana (Sarra KAMOUN)</t>
+          <t xml:space="preserve">Lolita (Syrine BEN SBIHA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D100">
+        <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C100">
+      <c t="inlineStr" r="E100">
         <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D100">
+      <c t="inlineStr" r="F100">
         <is>
           <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E100">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F100">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="G100">
         <is>
           <t xml:space="preserve">14h-23h</t>
@@ -4843,7 +4848,7 @@
       </c>
       <c t="inlineStr" r="H100">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I100">
@@ -4855,22 +4860,22 @@
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Lilly (Ibtihel BEN KHALIFA)</t>
+          <t xml:space="preserve">Ludmila  (Olfa ALLAYA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D101">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E101">
@@ -4880,44 +4885,44 @@
       </c>
       <c t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G101">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H101">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="I101">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Lolita (Syrine BEN SBIHA)</t>
+          <t xml:space="preserve">Luigy (Med taieb MANAI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D102">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E102">
@@ -4927,17 +4932,17 @@
       </c>
       <c t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G102">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H102">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I102">
@@ -4949,79 +4954,79 @@
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Ludmila  (Olfa ALLAYA)</t>
+          <t xml:space="preserve">Luna (Alyssa BEN ABDERRAZEK)</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h R 2h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D103">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">R 17h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E103">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G103">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H103">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I103">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Luigy (Med taieb MANAI)</t>
+          <t xml:space="preserve">Lyna (Lamia BRAHAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">R 17h-23h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">F 16h-17h 18h-3h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D104">
         <is>
-          <t xml:space="preserve">F 16h-17h 18h-3h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E104">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G104">
@@ -5031,123 +5036,123 @@
       </c>
       <c t="inlineStr" r="H104">
         <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I104">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Luna (Alyssa BEN ABDERRAZEK)</t>
+          <t xml:space="preserve">Mabrouka (Mabrouka HANZOULI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D105">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E105">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="G105">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">11h-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I105">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Lyna (Lamia BRAHAM)</t>
+          <t xml:space="preserve">Margot (Houda SELLAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">R 8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="D106">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E106">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G106">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">8h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I106">
+        <is>
+          <t xml:space="preserve">Cadre</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Mabrouka (Mabrouka HANZOULI)</t>
+          <t xml:space="preserve">Mary madison (Samia TAAMALLAH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D107">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E107">
@@ -5157,59 +5162,59 @@
       </c>
       <c t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G107">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">6h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I107">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Cadre</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Margot (Houda SELLAM)</t>
+          <t xml:space="preserve">Mathieu (Akram SBOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">14h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D108">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="E108">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G108">
         <is>
-          <t xml:space="preserve">8h-17h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H108">
@@ -5226,101 +5231,101 @@
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Mary madison (Samia TAAMALLAH)</t>
+          <t xml:space="preserve">Maylie (Marwa DHOUIOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D109">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E109">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">6h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G109">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H109">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I109">
         <is>
-          <t xml:space="preserve">Cadre</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Mathieu (Akram SBOUI)</t>
+          <t xml:space="preserve">Mika (Omar SAIDANE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">9h-19h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">9h-19h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D110">
         <is>
-          <t xml:space="preserve">9h-19h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E110">
         <is>
-          <t xml:space="preserve">9h-19h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">9h-19h</t>
+          <t xml:space="preserve">R 20h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G110">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 20h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I110">
         <is>
-          <t xml:space="preserve">Cadre</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Maylie (Marwa DHOUIOUI)</t>
+          <t xml:space="preserve">Miles (Ghaith AMRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
@@ -5330,12 +5335,12 @@
       </c>
       <c t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D111">
         <is>
-          <t xml:space="preserve">R 19h-21h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E111">
@@ -5345,12 +5350,12 @@
       </c>
       <c t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G111">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H111">
@@ -5367,42 +5372,42 @@
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Mika (Omar SAIDANE)</t>
+          <t xml:space="preserve">Mirta (Sawssen AMMAR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">R 14h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 10h-14h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D112">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 10h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="E112">
         <is>
-          <t xml:space="preserve">F 16h-17h 18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G112">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H112">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I112">
@@ -5414,64 +5419,64 @@
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Miles (Ghaith AMRI)</t>
+          <t xml:space="preserve">Nahed (Nahed ZAGUIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D113">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E113">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G113">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H113">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I113">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Comptable</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Mirta (Sawssen AMMAR)</t>
+          <t xml:space="preserve">Naomi (Malek DHOUIHRI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">R 17h-23h</t>
+          <t xml:space="preserve">R 17h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D114">
@@ -5491,7 +5496,7 @@
       </c>
       <c t="inlineStr" r="G114">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H114">
@@ -5508,89 +5513,89 @@
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">Nahed (Nahed ZAGUIA)</t>
+          <t xml:space="preserve">Nesrine (Nesrine BEN KHALIFA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D115">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E115">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">8h-17h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G115">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I115">
         <is>
-          <t xml:space="preserve">Comptable</t>
+          <t xml:space="preserve">Femme de ménage</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Naomi (Malek DHOUIHRI)</t>
+          <t xml:space="preserve">Nicolas (Med ali KTITA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">9h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D116">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">9h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E116">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">9h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G116">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">9h-17h30</t>
         </is>
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I116">
@@ -5602,27 +5607,27 @@
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Nesrine (Nesrine BEN KHALIFA)</t>
+          <t xml:space="preserve">Nikki (Bochra BEN ROMDHANE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D117">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E117">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F117">
@@ -5632,39 +5637,39 @@
       </c>
       <c t="inlineStr" r="G117">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H117">
         <is>
-          <t xml:space="preserve">11h-20h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I117">
         <is>
-          <t xml:space="preserve">Femme de ménage</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Nicolas (Med ali KTITA)</t>
+          <t xml:space="preserve">Norbert (Nader CHADLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D118">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E118">
@@ -5679,59 +5684,59 @@
       </c>
       <c t="inlineStr" r="G118">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I118">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Nikki (Bochra BEN ROMDHANE)</t>
+          <t xml:space="preserve">Nourane (Saida KAROUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">R 14h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D119">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E119">
         <is>
-          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G119">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I119">
@@ -5743,22 +5748,22 @@
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Norbert (Nader CHADLI)</t>
+          <t xml:space="preserve">Orianne (Meryam MOSREF)</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h R 21h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="D120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 9h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E120">
@@ -5768,54 +5773,54 @@
       </c>
       <c t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="G120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="H120">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="I120">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Nourane (Saida KAROUI)</t>
+          <t xml:space="preserve">Oscar (Karim TRIFI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
+          <t xml:space="preserve">13h-22h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
           <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
-      <c t="inlineStr" r="C121">
+      <c t="inlineStr" r="D121">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E121">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F121">
         <is>
           <t xml:space="preserve">13h-22h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D121">
-        <is>
-          <t xml:space="preserve">13h-22h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E121">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F121">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G121">
@@ -5837,79 +5842,79 @@
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Orianne (Meryam MOSREF)</t>
+          <t xml:space="preserve">Oussema (Oussama ELKHARAT)</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="D122">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="E122">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="G122">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="H122">
         <is>
-          <t xml:space="preserve">9h-18h</t>
+          <t xml:space="preserve">OFF</t>
         </is>
       </c>
       <c t="inlineStr" r="I122">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Dirigeant</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">Oscar (Karim TRIFI)</t>
+          <t xml:space="preserve">Pablo (Becheur BOURAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 14h-15h 15h-0h R 0h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D123">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E123">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G123">
@@ -5919,7 +5924,7 @@
       </c>
       <c t="inlineStr" r="H123">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I123">
@@ -5931,89 +5936,89 @@
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Oussema (Oussama ELKHARAT)</t>
+          <t xml:space="preserve">Paolo (Mohamed hedi MARRAKCHI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">R 17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H124">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">17h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="I124">
         <is>
-          <t xml:space="preserve">Dirigeant</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">Pablo (Becheur BOURAOUI)</t>
+          <t xml:space="preserve">Percey (Ahmed CHAABENI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">F 13h-14h 14h-23h</t>
+          <t xml:space="preserve">V 15h-18h R 18h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">V 14h30-20h</t>
         </is>
       </c>
       <c t="inlineStr" r="D125">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E125">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G125">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H125">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I125">
@@ -6025,17 +6030,17 @@
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Paolo (Mohamed hedi MARRAKCHI)</t>
+          <t xml:space="preserve">Petra (Halima MADHBOUH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">16h-1h R 1h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D126">
@@ -6045,69 +6050,69 @@
       </c>
       <c t="inlineStr" r="E126">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G126">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H126">
         <is>
-          <t xml:space="preserve">17h-3h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I126">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">Percey (Ahmed CHAABENI)</t>
+          <t xml:space="preserve">Ramon (Khaled RAHMANI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">15h-0h R+ 0h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">R 15h30-17h30 R 19h05-21h05</t>
         </is>
       </c>
       <c t="inlineStr" r="D127">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E127">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G127">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H127">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I127">
@@ -6119,89 +6124,89 @@
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">Petra (Halima MADHBOUH)</t>
+          <t xml:space="preserve">Raven (Asma HAMROUNI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="D128">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E128">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="G128">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-17h</t>
         </is>
       </c>
       <c t="inlineStr" r="H128">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I128">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable de production</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Ramon (Khaled RAHMANI)</t>
+          <t xml:space="preserve">Reine (Jihen GUESMI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">14h-23h P 16h50-23h</t>
+          <t xml:space="preserve">R 19h-0h CH 19h-0h CH 0h-2h R 0h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D129">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E129">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G129">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">17h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H129">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I129">
@@ -6213,89 +6218,89 @@
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">Raven (Asma HAMROUNI)</t>
+          <t xml:space="preserve">Reza (Safa RAGGUEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D130">
         <is>
-          <t xml:space="preserve">7h-17h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E130">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">16h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G130">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R+ 14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H130">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I130">
         <is>
-          <t xml:space="preserve">Responsable de production</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">Reine (Jihen GUESMI)</t>
+          <t xml:space="preserve">Rick (Souhail GASMIA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">CH 18h-0h R 18h-0h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D131">
         <is>
-          <t xml:space="preserve">CH 18h-0h R 18h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E131">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G131">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H131">
         <is>
-          <t xml:space="preserve">17h-2h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I131">
@@ -6307,42 +6312,42 @@
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Reza (Safa RAGGUEM)</t>
+          <t xml:space="preserve">Rubi (Nour REZGUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 21h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="D132">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">19h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="E132">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">19h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">19h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="G132">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">19h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="H132">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">19h-2h</t>
         </is>
       </c>
       <c t="inlineStr" r="I132">
@@ -6354,32 +6359,32 @@
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Rick (Souhail GASMIA)</t>
+          <t xml:space="preserve">Sahar (Sahar FEKIH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="D133">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E133">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h30-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G133">
@@ -6394,49 +6399,49 @@
       </c>
       <c t="inlineStr" r="I133">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Comptable</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Rubi (Nour REZGUI)</t>
+          <t xml:space="preserve">Salvadore (Omar RIDEN)</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">23h-6h</t>
+          <t xml:space="preserve">R 17h-0h R 0h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 17h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D134">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">F 15h-16h 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E134">
         <is>
-          <t xml:space="preserve">23h-6h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">23h-6h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G134">
         <is>
-          <t xml:space="preserve">23h-6h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H134">
         <is>
-          <t xml:space="preserve">23h-6h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I134">
@@ -6448,74 +6453,74 @@
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Sahar (Sahar FEKIH)</t>
+          <t xml:space="preserve">Sia (Cyrine BEN CHEIKH MOHAMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D135">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E135">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">8h30-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G135">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H135">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I135">
         <is>
-          <t xml:space="preserve">Comptable</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Salvadore (Omar RIDEN)</t>
+          <t xml:space="preserve">Silas (Hamdi GHARRAD)</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">F 15h-16h 16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="D136">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E136">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F136">
@@ -6525,12 +6530,12 @@
       </c>
       <c t="inlineStr" r="G136">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H136">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="I136">
@@ -6542,153 +6547,148 @@
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Sia (Cyrine BEN CHEIKH MOHAMED)</t>
+          <t xml:space="preserve">Simone (Lamia BRAHAM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="D137">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E137">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">CONGÉ PAYÉ</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G137">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H137">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h30-15h30</t>
         </is>
       </c>
       <c t="inlineStr" r="I137">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Silas (Hamdi GHARRAD)</t>
+          <t xml:space="preserve">Stacey (Rania GRABA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D138">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E138">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G138">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H138">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">15h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I138">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Responsable voyant</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Simone (Lamia BRAHAM)</t>
+          <t xml:space="preserve">Stella (Nahla AYADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D139">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="E139">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
       <c t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G139">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H139">
         <is>
-          <t xml:space="preserve">7h30-15h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I139">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">12h-21h</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Stacey (Rania GRABA)</t>
+          <t xml:space="preserve">Steve (Seif BEN CHEIKH MOHAMED)</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C140">
@@ -6698,49 +6698,49 @@
       </c>
       <c t="inlineStr" r="D140">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="E140">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="G140">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">23h-7h</t>
         </is>
       </c>
       <c t="inlineStr" r="H140">
         <is>
-          <t xml:space="preserve">15h-1h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I140">
         <is>
-          <t xml:space="preserve">Responsable voyant</t>
+          <t xml:space="preserve">Phoning</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Stella (Nahla AYADI)</t>
+          <t xml:space="preserve">Suzy (Fatma GHEDIRA)</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D141">
@@ -6750,64 +6750,69 @@
       </c>
       <c t="inlineStr" r="E141">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G141">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H141">
         <is>
-          <t xml:space="preserve">12h-21h</t>
+          <t xml:space="preserve">8h-15h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I141">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Steve (Seif BEN CHEIKH MOHAMED)</t>
+          <t xml:space="preserve">Sylvia (Souha MISSAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D142">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="E142">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="G142">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">7h-16h</t>
         </is>
       </c>
       <c t="inlineStr" r="H142">
         <is>
-          <t xml:space="preserve">23h-7h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I142">
@@ -6819,37 +6824,37 @@
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Suzy (Fatma GHEDIRA)</t>
+          <t xml:space="preserve">Theresa (Wafa OUESLETI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 22h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D143">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="E143">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">8h-15h</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="G143">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">18h-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="H143">
@@ -6866,54 +6871,54 @@
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Sylvia (Souha MISSAOUI)</t>
+          <t xml:space="preserve">Tobias (Slim YAHYAOUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D144">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="E144">
         <is>
-          <t xml:space="preserve">R+ 15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">R 6h-12h</t>
         </is>
       </c>
       <c t="inlineStr" r="G144">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H144">
         <is>
-          <t xml:space="preserve">7h-16h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I144">
         <is>
-          <t xml:space="preserve">Phoning</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Theresa (Wafa OUESLETI)</t>
+          <t xml:space="preserve">Tommy (Nizar SOUILEM)</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
@@ -6923,22 +6928,22 @@
       </c>
       <c t="inlineStr" r="C145">
         <is>
+          <t xml:space="preserve">R 15h-18h 18h-3h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D145">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E145">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F145">
+        <is>
           <t xml:space="preserve">18h-3h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D145">
-        <is>
-          <t xml:space="preserve">18h-3h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E145">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F145">
-        <is>
-          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G145">
@@ -6960,24 +6965,24 @@
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Tobias (Slim YAHYAOUI)</t>
+          <t xml:space="preserve">Tony (Nabil MANSOURI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D146">
+        <is>
           <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C146">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D146">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="E146">
         <is>
           <t xml:space="preserve">6h-15h</t>
@@ -6985,64 +6990,64 @@
       </c>
       <c t="inlineStr" r="F146">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G146">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H146">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I146">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Rédacteur mail</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Tommy (Nizar SOUILEM)</t>
+          <t xml:space="preserve">Tova (Asma CHOUCHENE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="D147">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E147">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">18h-3h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G147">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H147">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I147">
@@ -7054,12 +7059,12 @@
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Tony (Nabil MANSOURI)</t>
+          <t xml:space="preserve">Travis (Mohamed BEN HFAIEDH)</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C148">
@@ -7074,7 +7079,7 @@
       </c>
       <c t="inlineStr" r="E148">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F148">
@@ -7084,54 +7089,54 @@
       </c>
       <c t="inlineStr" r="G148">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H148">
         <is>
-          <t xml:space="preserve">6h-15h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="I148">
         <is>
-          <t xml:space="preserve">Rédacteur mail</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Tova (Asma CHOUCHENE)</t>
+          <t xml:space="preserve">Troy (Ala BOUZID)</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">R 18h-20h</t>
+          <t xml:space="preserve">R 18h30-22h18</t>
         </is>
       </c>
       <c t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D149">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="E149">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="G149">
         <is>
-          <t xml:space="preserve">R 18h-20h</t>
+          <t xml:space="preserve">14h-23h</t>
         </is>
       </c>
       <c t="inlineStr" r="H149">
@@ -7148,17 +7153,17 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Travis (Mohamed BEN HFAIEDH)</t>
+          <t xml:space="preserve">Ursula (Najia anouar DERBEZ)</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+          <t xml:space="preserve">5h-14h P 12h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="D150">
@@ -7168,22 +7173,22 @@
       </c>
       <c t="inlineStr" r="E150">
         <is>
-          <t xml:space="preserve">F 14h-15h 15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="G150">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="H150">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">5h-14h</t>
         </is>
       </c>
       <c t="inlineStr" r="I150">
@@ -7195,42 +7200,42 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Troy (Ala BOUZID)</t>
+          <t xml:space="preserve">Vanessa (Olfa CHOUAIEB)</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">R 23h30-3h</t>
         </is>
       </c>
       <c t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="D151">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="E151">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="G151">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">15h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="H151">
         <is>
-          <t xml:space="preserve">14h-23h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="I151">
@@ -7242,42 +7247,42 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Ursula (Najia anouar DERBEZ)</t>
+          <t xml:space="preserve">Vladimir (Nessim HAJJI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">R 5h-14h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D152">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E152">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">5h-14h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="G152">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="H152">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I152">
@@ -7289,79 +7294,74 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Vanessa (Olfa CHOUAIEB)</t>
+          <t xml:space="preserve">Voy_test_deux (Voy PRODTEST)</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D153">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E153">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F153">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G153">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H153">
         <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I153">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Vladimir (Nessim HAJJI)</t>
+          <t xml:space="preserve">Voy_test_trois (Voy PRODTEST)</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">ABSENCE</t>
         </is>
       </c>
       <c t="inlineStr" r="D154">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="E154">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">16h-1h</t>
+          <t xml:space="preserve">8h-18h</t>
         </is>
       </c>
       <c t="inlineStr" r="G154">
@@ -7383,74 +7383,79 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Voy_test_deux (Voy PRODTEST)</t>
+          <t xml:space="preserve">Whitney (Ghofran NASRALLI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">15h-0h CH 16h-0h</t>
         </is>
       </c>
       <c t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">16h-1h CH 16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D155">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E155">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="G155">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="H155">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I155">
+        <is>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Voy_test_trois (Voy PRODTEST)</t>
+          <t xml:space="preserve">Yadira (Mayssa KAROUI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">ABSENCE</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="D156">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="E156">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">8h-18h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G156">
@@ -7460,7 +7465,7 @@
       </c>
       <c t="inlineStr" r="H156">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">13h-22h</t>
         </is>
       </c>
       <c t="inlineStr" r="I156">
@@ -7472,79 +7477,79 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Wafa (Wafa HICHRI)</t>
+          <t xml:space="preserve">Yann (Mhamed KEDADI)</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
+          <t xml:space="preserve">9h-18h R 18h-19h R 19h-20h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">9h-18h R 18h-19h R 19h-20h</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D157">
+        <is>
           <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
-      <c t="inlineStr" r="C157">
+      <c t="inlineStr" r="E157">
         <is>
           <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
-      <c t="inlineStr" r="D157">
+      <c t="inlineStr" r="F157">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G157">
+        <is>
+          <t xml:space="preserve">REPOS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H157">
         <is>
           <t xml:space="preserve">9h-18h</t>
         </is>
       </c>
-      <c t="inlineStr" r="E157">
-        <is>
-          <t xml:space="preserve">9h-18h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F157">
-        <is>
-          <t xml:space="preserve">9h-18h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G157">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H157">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
       <c t="inlineStr" r="I157">
         <is>
-          <t xml:space="preserve">Chargé de recrutement</t>
+          <t xml:space="preserve">Téléconseiller</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Whitney (Ghofran NASRALLI)</t>
+          <t xml:space="preserve">Yasser (Yesser NCIR)</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">CH 15h15-21h15 R 15h15-21h15</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="D158">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">7h30-16h30</t>
         </is>
       </c>
       <c t="inlineStr" r="E158">
         <is>
-          <t xml:space="preserve">13h-22h CH 13h-22h</t>
+          <t xml:space="preserve">10h-19h</t>
         </is>
       </c>
       <c t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">CH 13h-22h 13h-22h</t>
+          <t xml:space="preserve">7h30-16h30</t>
         </is>
       </c>
       <c t="inlineStr" r="G158">
@@ -7559,49 +7564,49 @@
       </c>
       <c t="inlineStr" r="I158">
         <is>
-          <t xml:space="preserve">Téléconseiller</t>
+          <t xml:space="preserve">Technicien</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Yadira (Mayssa KAROUI)</t>
+          <t xml:space="preserve">Zayn (Hamza BOUALLEGUE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="D159">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="E159">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="G159">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">13h-22h</t>
+          <t xml:space="preserve">16h-1h</t>
         </is>
       </c>
       <c t="inlineStr" r="I159">
@@ -7613,22 +7618,22 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">Yann (Mhamed KEDADI)</t>
+          <t xml:space="preserve">Zen (Bahaa eddine BELHOUCHE)</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="D160">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">REPOS</t>
         </is>
       </c>
       <c t="inlineStr" r="E160">
@@ -7638,161 +7643,20 @@
       </c>
       <c t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">REPOS</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="G160">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="H160">
         <is>
-          <t xml:space="preserve">15h-0h</t>
+          <t xml:space="preserve">6h-15h</t>
         </is>
       </c>
       <c t="inlineStr" r="I160">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c t="inlineStr" r="A161">
-        <is>
-          <t xml:space="preserve">Yasser (Yesser NCIR)</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B161">
-        <is>
-          <t xml:space="preserve">9h30-18h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C161">
-        <is>
-          <t xml:space="preserve">9h30-18h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D161">
-        <is>
-          <t xml:space="preserve">9h30-18h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E161">
-        <is>
-          <t xml:space="preserve">9h30-18h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F161">
-        <is>
-          <t xml:space="preserve">9h30-18h30</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G161">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H161">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I161">
-        <is>
-          <t xml:space="preserve">Technicien</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c t="inlineStr" r="A162">
-        <is>
-          <t xml:space="preserve">Zayn (Hamza BOUALLEGUE)</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B162">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C162">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D162">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E162">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F162">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G162">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H162">
-        <is>
-          <t xml:space="preserve">15h-0h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I162">
-        <is>
-          <t xml:space="preserve">Téléconseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c t="inlineStr" r="A163">
-        <is>
-          <t xml:space="preserve">Zen (Bahaa eddine BELHOUCHE)</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B163">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C163">
-        <is>
-          <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D163">
-        <is>
-          <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E163">
-        <is>
-          <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F163">
-        <is>
-          <t xml:space="preserve">6h-15h</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G163">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H163">
-        <is>
-          <t xml:space="preserve">REPOS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I163">
         <is>
           <t xml:space="preserve">Téléconseiller</t>
         </is>
